--- a/DesheTools/configuration/fields.xlsx
+++ b/DesheTools/configuration/fields.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tauex-my.sharepoint.com/personal/yoskoyoav_tauex_tau_ac_il/Documents/Utilities/Deshe-1.2.1/DesheTools/configuration/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dedi\Desktop\עבודה\My GIS\דשא\Github - Deshe\Deshe\DesheTools\configuration\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{EF3EE125-6BE6-406A-9B7E-1002C3A53CA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D779C19B-DA05-4249-ACF6-83258C9E8EA8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="642" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" tabRatio="642" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="fields" sheetId="1" r:id="rId1"/>
@@ -1660,7 +1660,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1685,7 +1685,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1693,7 +1693,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -7941,7 +7941,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="236" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A236" s="43">
         <v>50066</v>
       </c>
@@ -47330,7 +47330,7 @@
     <tabColor theme="0" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="37.5703125" style="88" customWidth="1"/>
     <col min="2" max="2" width="35.140625" style="88" customWidth="1"/>
@@ -47341,7 +47341,7 @@
     <col min="7" max="16384" width="10" style="88"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="88" t="s">
         <v>419</v>
       </c>
@@ -47361,7 +47361,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="88" t="str">
         <f>VLOOKUP(D2,fields!A:D,2,FALSE)</f>
         <v>points</v>
@@ -47384,7 +47384,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="88" t="str">
         <f>VLOOKUP(D3,fields!A:D,2,FALSE)</f>
         <v>points</v>
@@ -47407,7 +47407,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="88" t="str">
         <f>VLOOKUP(D4,fields!A:D,2,FALSE)</f>
         <v>points</v>
@@ -47430,7 +47430,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="88" t="str">
         <f>VLOOKUP(D5,fields!A:D,2,FALSE)</f>
         <v>points</v>
@@ -47453,7 +47453,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="88" t="str">
         <f>VLOOKUP(D6,fields!A:D,2,FALSE)</f>
         <v>points</v>
@@ -47476,7 +47476,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="88" t="str">
         <f>VLOOKUP(D7,fields!A:D,2,FALSE)</f>
         <v>points</v>
@@ -47499,7 +47499,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="88" t="str">
         <f>VLOOKUP(D8,fields!A:D,2,FALSE)</f>
         <v>points</v>
@@ -47522,7 +47522,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="88" t="str">
         <f>VLOOKUP(D9,fields!A:D,2,FALSE)</f>
         <v>points</v>
@@ -47545,7 +47545,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="88" t="str">
         <f>VLOOKUP(D10,fields!A:D,2,FALSE)</f>
         <v>points</v>
@@ -47568,7 +47568,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="88" t="str">
         <f>VLOOKUP(D11,fields!A:D,2,FALSE)</f>
         <v>points</v>
@@ -47591,7 +47591,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="88" t="str">
         <f>VLOOKUP(D12,fields!A:D,2,FALSE)</f>
         <v>points</v>
@@ -47614,7 +47614,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="88" t="str">
         <f>VLOOKUP(D13,fields!A:D,2,FALSE)</f>
         <v>points_PlantTypeCoverDistribut</v>
@@ -47637,7 +47637,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="88" t="str">
         <f>VLOOKUP(D14,fields!A:D,2,FALSE)</f>
         <v>points_PlantTypeCoverDistribut</v>
@@ -47660,7 +47660,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="88" t="str">
         <f>VLOOKUP(D15,fields!A:D,2,FALSE)</f>
         <v>points_PlantTypeCoverDistribut</v>
@@ -47683,7 +47683,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="88" t="str">
         <f>VLOOKUP(D16,fields!A:D,2,FALSE)</f>
         <v>points_PlantTypeCoverDistribut</v>
@@ -47706,7 +47706,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="88" t="str">
         <f>VLOOKUP(D17,fields!A:D,2,FALSE)</f>
         <v>points_PlantTypeCoverDistribut</v>
@@ -49369,7 +49369,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="58" spans="1:10" s="20" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" s="20" customFormat="1" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A58" s="43">
         <v>50089</v>
       </c>
@@ -49541,7 +49541,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="64" spans="1:10" s="20" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" s="20" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A64" s="43">
         <v>50064</v>
       </c>
@@ -49601,7 +49601,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="66" spans="1:10" s="20" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10" s="20" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A66" s="43">
         <v>50066</v>
       </c>

--- a/DesheTools/configuration/fields.xlsx
+++ b/DesheTools/configuration/fields.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{EF3EE125-6BE6-406A-9B7E-1002C3A53CA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D779C19B-DA05-4249-ACF6-83258C9E8EA8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" tabRatio="642" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" tabRatio="642" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="fields" sheetId="1" r:id="rId1"/>
@@ -2536,93 +2536,6 @@
       <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -2783,6 +2696,93 @@
       <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FF7030A0"/>
@@ -2819,47 +2819,47 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E43E37A3-7B67-4000-A29A-CE671685306A}" name="fields" displayName="fields" ref="A1:G297" totalsRowShown="0" dataDxfId="63">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E43E37A3-7B67-4000-A29A-CE671685306A}" name="fields" displayName="fields" ref="A1:G297" totalsRowShown="0" dataDxfId="51">
   <autoFilter ref="A1:G297" xr:uid="{E43E37A3-7B67-4000-A29A-CE671685306A}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{55F41C63-F033-407F-8E01-E15B9BD574B1}" name="code" dataDxfId="62"/>
-    <tableColumn id="5" xr3:uid="{1B1F22C4-6894-4A74-B995-BF7E12179554}" name="tableName(notinuse)" dataDxfId="61"/>
-    <tableColumn id="6" xr3:uid="{BC5762C9-B87A-4B20-AD71-A0A1FC810E83}" name="name" dataDxfId="60"/>
-    <tableColumn id="7" xr3:uid="{309EBD7E-6D91-48B2-94D1-BC70B1DF8A77}" name="alias" dataDxfId="59"/>
-    <tableColumn id="8" xr3:uid="{B99BA1E5-DE93-44AF-A80A-FA552F7C467E}" name="type" dataDxfId="58"/>
-    <tableColumn id="9" xr3:uid="{D91B622A-BC37-462F-88A9-43A56800D108}" name="domain" dataDxfId="57"/>
-    <tableColumn id="10" xr3:uid="{D10D8FE1-FC3F-4320-8041-944BACE6386A}" name="length" dataDxfId="56"/>
+    <tableColumn id="1" xr3:uid="{55F41C63-F033-407F-8E01-E15B9BD574B1}" name="code" dataDxfId="50"/>
+    <tableColumn id="5" xr3:uid="{1B1F22C4-6894-4A74-B995-BF7E12179554}" name="tableName(notinuse)" dataDxfId="49"/>
+    <tableColumn id="6" xr3:uid="{BC5762C9-B87A-4B20-AD71-A0A1FC810E83}" name="name" dataDxfId="48"/>
+    <tableColumn id="7" xr3:uid="{309EBD7E-6D91-48B2-94D1-BC70B1DF8A77}" name="alias" dataDxfId="47"/>
+    <tableColumn id="8" xr3:uid="{B99BA1E5-DE93-44AF-A80A-FA552F7C467E}" name="type" dataDxfId="46"/>
+    <tableColumn id="9" xr3:uid="{D91B622A-BC37-462F-88A9-43A56800D108}" name="domain" dataDxfId="45"/>
+    <tableColumn id="10" xr3:uid="{D10D8FE1-FC3F-4320-8041-944BACE6386A}" name="length" dataDxfId="44"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9AC58631-8B18-47DD-880B-CB14E18DB306}" name="classification" displayName="classification" ref="A1:J297" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9AC58631-8B18-47DD-880B-CB14E18DB306}" name="classification" displayName="classification" ref="A1:J297" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
   <autoFilter ref="A1:J297" xr:uid="{2B6FDA2F-EAB7-4D8A-BE34-7EA2F7A30E79}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{BE458E66-ADDE-4F2F-A00C-3B8D36E6DA4C}" name="code" dataDxfId="53"/>
-    <tableColumn id="2" xr3:uid="{2F52A7D4-F3EF-4C11-8E0E-3586433181E0}" name="tableName(notinuse)" dataDxfId="52">
+    <tableColumn id="1" xr3:uid="{BE458E66-ADDE-4F2F-A00C-3B8D36E6DA4C}" name="code" dataDxfId="61"/>
+    <tableColumn id="2" xr3:uid="{2F52A7D4-F3EF-4C11-8E0E-3586433181E0}" name="tableName(notinuse)" dataDxfId="60">
       <calculatedColumnFormula>IF(VLOOKUP($A2,fields[[code]:[length]],2,FALSE)=0, "", VLOOKUP($A2,fields[[code]:[length]],2,FALSE))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5F451E16-0DAC-4C13-B4BC-3C29ABEBB803}" name="name" dataDxfId="51">
+    <tableColumn id="3" xr3:uid="{5F451E16-0DAC-4C13-B4BC-3C29ABEBB803}" name="name" dataDxfId="59">
       <calculatedColumnFormula>IF(VLOOKUP($A2,fields[[code]:[length]],3,FALSE)=0, "", VLOOKUP($A2,fields[[code]:[length]],3,FALSE))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{0A872CE3-A266-493A-AD80-30F866530C95}" name="alias" dataDxfId="50">
+    <tableColumn id="4" xr3:uid="{0A872CE3-A266-493A-AD80-30F866530C95}" name="alias" dataDxfId="58">
       <calculatedColumnFormula>IF(VLOOKUP($A2,fields[[code]:[length]],4,FALSE)=0, "", VLOOKUP($A2,fields[[code]:[length]],4,FALSE))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{2D5370B3-6E0A-4C5C-858E-5918DB9DC6F8}" name="type" dataDxfId="49">
+    <tableColumn id="5" xr3:uid="{2D5370B3-6E0A-4C5C-858E-5918DB9DC6F8}" name="type" dataDxfId="57">
       <calculatedColumnFormula>IF(VLOOKUP($A2,fields[[code]:[length]],5,FALSE)=0, "", VLOOKUP($A2,fields[[code]:[length]],5,FALSE))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{4236AEE0-12E7-48F8-A97B-AC0E918EDFF8}" name="domain" dataDxfId="48">
+    <tableColumn id="6" xr3:uid="{4236AEE0-12E7-48F8-A97B-AC0E918EDFF8}" name="domain" dataDxfId="56">
       <calculatedColumnFormula>IF(VLOOKUP($A2,fields[[code]:[length]],6,FALSE)=0, "", VLOOKUP($A2,fields[[code]:[length]],6,FALSE))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{10E840B1-BCA0-4ACA-B740-659EB51586E2}" name="length" dataDxfId="47">
+    <tableColumn id="7" xr3:uid="{10E840B1-BCA0-4ACA-B740-659EB51586E2}" name="length" dataDxfId="55">
       <calculatedColumnFormula>IF(VLOOKUP($A2,fields[[code]:[length]],7,FALSE)=0, "", VLOOKUP($A2,fields[[code]:[length]],7,FALSE))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{064BC516-8D92-49D0-BA94-54CA56CF09AB}" name="toAdd" dataDxfId="46"/>
-    <tableColumn id="9" xr3:uid="{0B20B3C6-896E-462A-8A68-08BC8E4B9A26}" name="sequence" dataDxfId="45"/>
-    <tableColumn id="10" xr3:uid="{1086967F-2202-4B77-84FD-E427130A0924}" name="checkIfExists" dataDxfId="44"/>
+    <tableColumn id="8" xr3:uid="{064BC516-8D92-49D0-BA94-54CA56CF09AB}" name="toAdd" dataDxfId="54"/>
+    <tableColumn id="9" xr3:uid="{0B20B3C6-896E-462A-8A68-08BC8E4B9A26}" name="sequence" dataDxfId="53"/>
+    <tableColumn id="10" xr3:uid="{1086967F-2202-4B77-84FD-E427130A0924}" name="checkIfExists" dataDxfId="52"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
